--- a/survey_templates/043_high_school_student_climate_change_awareness_survey--survey_templates.xlsx
+++ b/survey_templates/043_high_school_student_climate_change_awareness_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -757,8 +757,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="49" customWidth="1" min="2" max="2"/>
+    <col width="49" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'very_concerned'}</t>
+          <t>very_concerned</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Very concerned'}</t>
+          <t>Very concerned</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_concerned'}</t>
+          <t>somewhat_concerned</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat concerned'}</t>
+          <t>Somewhat concerned</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'not_concerned_at_all'}</t>
+          <t>not_concerned_at_all</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Not concerned at all'}</t>
+          <t>Not concerned at all</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'carbon_emissions'}</t>
+          <t>carbon_emissions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Carbon emissions'}</t>
+          <t>Carbon emissions</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'deforestation'}</t>
+          <t>deforestation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Deforestation'}</t>
+          <t>Deforestation</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'burning_fossil_fuels'}</t>
+          <t>burning_fossil_fuels</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Burning fossil fuels'}</t>
+          <t>Burning fossil fuels</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'reduce_carbon_emissions'}</t>
+          <t>reduce_carbon_emissions</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Reduce carbon emissions'}</t>
+          <t>Reduce carbon emissions</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'invest_in_renewable_energy'}</t>
+          <t>invest_in_renewable_energy</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Invest in renewable energy'}</t>
+          <t>Invest in renewable energy</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'protect_and_restore_natural_habitats'}</t>
+          <t>protect_and_restore_natural_habitats</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Protect and restore natural habitats'}</t>
+          <t>Protect and restore natural habitats</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'lack_of_awareness'}</t>
+          <t>lack_of_awareness</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Lack of awareness'}</t>
+          <t>Lack of awareness</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'economic_costs'}</t>
+          <t>economic_costs</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Economic costs'}</t>
+          <t>Economic costs</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'government_policies'}</t>
+          <t>government_policies</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Government policies'}</t>
+          <t>Government policies</t>
         </is>
       </c>
     </row>
@@ -990,12 +990,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'very_likely'}</t>
+          <t>very_likely</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Very likely'}</t>
+          <t>Very likely</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_likely'}</t>
+          <t>somewhat_likely</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat likely'}</t>
+          <t>Somewhat likely</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'not_likely_at_all'}</t>
+          <t>not_likely_at_all</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Not likely at all'}</t>
+          <t>Not likely at all</t>
         </is>
       </c>
     </row>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'very_likely'}</t>
+          <t>very_likely</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Very likely'}</t>
+          <t>Very likely</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_likely'}</t>
+          <t>somewhat_likely</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat likely'}</t>
+          <t>Somewhat likely</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'not_likely_at_all'}</t>
+          <t>not_likely_at_all</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Not likely at all'}</t>
+          <t>Not likely at all</t>
         </is>
       </c>
     </row>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'educate_about_climate_change'}</t>
+          <t>educate_about_climate_change</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Educate about climate change'}</t>
+          <t>Educate about climate change</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'implement_sustainable_practices'}</t>
+          <t>implement_sustainable_practices</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Implement sustainable practices'}</t>
+          <t>Implement sustainable practices</t>
         </is>
       </c>
     </row>
@@ -1126,12 +1126,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'support_climate_change_research_and_development'}</t>
+          <t>support_climate_change_research_and_development</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Support climate change research and development'}</t>
+          <t>Support climate change research and development</t>
         </is>
       </c>
     </row>
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'classroom_instruction'}</t>
+          <t>classroom_instruction</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Classroom instruction'}</t>
+          <t>Classroom instruction</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'field_trips'}</t>
+          <t>field_trips</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Field trips'}</t>
+          <t>Field trips</t>
         </is>
       </c>
     </row>
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'online_resources'}</t>
+          <t>online_resources</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Online resources'}</t>
+          <t>Online resources</t>
         </is>
       </c>
     </row>
